--- a/test-output/projectResourcesOutputs/IdentifyCarWashingServices.xlsx
+++ b/test-output/projectResourcesOutputs/IdentifyCarWashingServices.xlsx
@@ -23,16 +23,10 @@
     <t>Car Washing Service Store Phone Number</t>
   </si>
   <si>
-    <t>Check Engines</t>
+    <t>MyTVS MultiBrand Car Service</t>
   </si>
   <si>
-    <t>09054028953</t>
-  </si>
-  <si>
-    <t>Wheeler Cleaner</t>
-  </si>
-  <si>
-    <t>09980260665</t>
+    <t>08296967446</t>
   </si>
   <si>
     <t>The Detailing Mafia Madhapur</t>
@@ -41,16 +35,22 @@
     <t>07411720454</t>
   </si>
   <si>
-    <t>Dettaglio Dose</t>
+    <t>Express Car Service</t>
   </si>
   <si>
-    <t>08123619946</t>
+    <t>07490053458</t>
   </si>
   <si>
-    <t>S V Motors - Luxury Car Service</t>
+    <t>Car Makeover Detailing Studio</t>
   </si>
   <si>
-    <t>08197564496</t>
+    <t>09724682654</t>
+  </si>
+  <si>
+    <t>Ark Tyres And Car Decors</t>
+  </si>
+  <si>
+    <t>09972277399</t>
   </si>
 </sst>
 </file>

--- a/test-output/projectResourcesOutputs/IdentifyCarWashingServices.xlsx
+++ b/test-output/projectResourcesOutputs/IdentifyCarWashingServices.xlsx
@@ -29,16 +29,16 @@
     <t>08296967446</t>
   </si>
   <si>
-    <t>The Detailing Mafia Madhapur</t>
+    <t>Check Engines</t>
   </si>
   <si>
-    <t>07411720454</t>
+    <t>09054028953</t>
   </si>
   <si>
-    <t>Express Car Service</t>
+    <t>S V Motors - Luxury Car Service</t>
   </si>
   <si>
-    <t>07490053458</t>
+    <t>08197564496</t>
   </si>
   <si>
     <t>Car Makeover Detailing Studio</t>
@@ -47,10 +47,10 @@
     <t>09724682654</t>
   </si>
   <si>
-    <t>Ark Tyres And Car Decors</t>
+    <t>Mm Teflon Coating</t>
   </si>
   <si>
-    <t>09972277399</t>
+    <t>08123098673</t>
   </si>
 </sst>
 </file>
